--- a/web/demo/2026-06_ledger_20260701-0911.xlsx
+++ b/web/demo/2026-06_ledger_20260701-0911.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FAF7F2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E5B45"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +55,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,69 +425,84 @@
   </sheetPr>
   <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>transaction_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>날짜</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>결제처</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>카테고리</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>결제수단</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>결제구분</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>원거래통화</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>원거래금액</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>source_type</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>collect_status</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>구매항목</t>
         </is>
@@ -524,8 +549,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -536,7 +559,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -579,8 +601,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -591,7 +611,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -634,8 +653,6 @@
           <t>법인결제</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -646,7 +663,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -674,7 +690,6 @@
           <t>식대</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>우리카드</t>
@@ -685,8 +700,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -697,7 +710,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -740,8 +752,6 @@
           <t>법인결제</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -752,7 +762,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -795,8 +804,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -807,7 +814,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -835,7 +841,6 @@
           <t>식대</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>국민카드</t>
@@ -846,8 +851,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -858,7 +861,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -886,7 +888,6 @@
           <t>구독료</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>국민카드</t>
@@ -897,8 +898,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -909,7 +908,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -952,8 +950,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -964,7 +960,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1007,8 +1002,6 @@
           <t>법인결제</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1019,7 +1012,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1047,7 +1039,6 @@
           <t>교육비</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>국민카드</t>
@@ -1058,8 +1049,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>receipt</t>
@@ -1102,7 +1091,6 @@
           <t>식대</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>우리카드</t>
@@ -1113,8 +1101,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1125,7 +1111,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1168,8 +1153,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1180,7 +1163,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1223,8 +1205,6 @@
           <t>법인결제</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1235,7 +1215,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1278,8 +1257,6 @@
           <t>법인결제</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1290,7 +1267,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1318,7 +1294,6 @@
           <t>식대</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>국민카드</t>
@@ -1329,8 +1304,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1341,7 +1314,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1384,8 +1356,6 @@
           <t>법인결제</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1396,7 +1366,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1439,8 +1408,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1451,7 +1418,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1494,8 +1460,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1506,7 +1470,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1534,7 +1497,6 @@
           <t>소모품비</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>신한법인카드</t>
@@ -1545,8 +1507,6 @@
           <t>법인결제</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>receipt</t>
@@ -1589,7 +1549,6 @@
           <t>기타물품</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>국민카드</t>
@@ -1600,8 +1559,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>receipt</t>
@@ -1679,7 +1636,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1722,8 +1678,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1734,7 +1688,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1762,7 +1715,6 @@
           <t>식대</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>하나카드</t>
@@ -1773,8 +1725,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>receipt</t>
@@ -1817,7 +1767,6 @@
           <t>식대</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>우리카드</t>
@@ -1828,8 +1777,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>receipt</t>
@@ -1872,7 +1819,6 @@
           <t>식대</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>하나카드</t>
@@ -1883,8 +1829,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1895,7 +1839,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1938,8 +1881,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1950,7 +1891,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1993,8 +1933,6 @@
           <t>법인결제</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -2005,7 +1943,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2048,8 +1985,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -2060,7 +1995,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2088,7 +2022,6 @@
           <t>복리후생비</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>신한법인카드</t>
@@ -2099,8 +2032,6 @@
           <t>법인결제</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>receipt</t>
@@ -2143,7 +2074,6 @@
           <t>식대</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>국민카드</t>
@@ -2154,8 +2084,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -2166,7 +2094,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2209,8 +2136,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -2221,7 +2146,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2249,7 +2173,6 @@
           <t>교통비</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>우리카드</t>
@@ -2260,8 +2183,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -2272,7 +2193,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2315,8 +2235,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -2327,7 +2245,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2355,7 +2272,6 @@
           <t>식대</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>우리카드</t>
@@ -2366,8 +2282,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -2378,7 +2292,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2421,8 +2334,6 @@
           <t>법인결제</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>manual</t>
@@ -2433,7 +2344,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2476,8 +2386,6 @@
           <t>법인결제</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -2488,7 +2396,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2516,7 +2423,6 @@
           <t>구독료</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>국민카드</t>
@@ -2527,8 +2433,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -2539,7 +2443,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2582,8 +2485,6 @@
           <t>법인결제</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -2594,7 +2495,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2637,8 +2537,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -2649,7 +2547,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
